--- a/etf_holdings/2026-09-04_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-04_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB12"/>
+  <dimension ref="A1:BL15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,200 +489,250 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>00403A_異動類型</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>00403A_調整方向</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>00403A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>00403A_權重_今日</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>00403A_權重變化</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>00403A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>00403A_股數_今日</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>00403A_股數變化</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>00985A_異動類型</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>00985A_調整方向</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>00985A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>00985A_權重_昨日</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>00985A_權重_今日</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>00985A_權重變化</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>00985A_股數_昨日</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>00985A_股數_今日</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>00985A_股數變化</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>00992A_異動類型</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>00992A_調整方向</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>00992A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>00992A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>00992A_權重_昨日</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>00992A_權重_今日</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>00992A_權重變化</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>00992A_股數_昨日</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>00992A_股數_今日</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>00992A_股數變化</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>00407A_異動類型</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>00407A_調整方向</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>00407A_權重_昨日</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>00407A_權重_今日</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>00407A_權重變化</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>00407A_股數_昨日</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>00407A_股數_今日</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>00407A_股數變化</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>00993A_異動類型</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>00993A_調整方向</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>00993A_權重_昨日</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>00993A_權重_今日</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>00993A_權重變化</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>00993A_股數_昨日</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>00993A_股數_今日</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>00993A_股數變化</t>
         </is>
@@ -753,62 +803,62 @@
           <t>20,000</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>健策精密工業</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>健策精密工業</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1.48%</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.98%</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>-0.50%</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="AF2" t="n">
         <v>27000</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AG2" t="n">
         <v>18000</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>-9,000</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
@@ -819,48 +869,58 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr">
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>健策</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>健策</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>1.30%</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>1.25%</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>-0.05%</t>
         </is>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BJ2" t="n">
         <v>23000</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BK2" t="n">
         <v>22000</v>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>-1,000</t>
         </is>
@@ -869,12 +929,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -882,7 +942,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00403A,00407A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -907,38 +967,38 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>383000</v>
+        <v>300000</v>
       </c>
       <c r="W3" t="n">
-        <v>295000</v>
+        <v>191000</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-88,000</t>
+          <t>-109,000</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -968,55 +1028,65 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>167000</v>
+        <v>177000</v>
       </c>
       <c r="BA3" t="n">
-        <v>165000</v>
+        <v>277000</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2,000</t>
-        </is>
-      </c>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1024,7 +1094,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
+          <t>00985A,00993A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1047,118 +1117,128 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>2.33%</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>1.94%</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>-0.39%</t>
-        </is>
-      </c>
-      <c r="AP4" t="n">
-        <v>513000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>441000</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-72,000</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1.97%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>-0.51%</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>383000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>295000</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-88,000</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>金像電子</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>金像電子</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>2.28%</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>2.22%</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>-0.06%</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>198000</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>200000</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>2,000</t>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.85%</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>167000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>165000</v>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>-2,000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1166,7 +1246,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00407A,00985A</t>
+          <t>00403A,00993A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1191,38 +1271,38 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>193000</v>
+        <v>2000000</v>
       </c>
       <c r="W5" t="n">
-        <v>105000</v>
+        <v>1000000</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-88,000</t>
+          <t>-1,000,000</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1235,52 +1315,16 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>1.19%</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>0.92%</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>-0.27%</t>
-        </is>
-      </c>
-      <c r="AP5" t="n">
-        <v>595000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>485000</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-110,000</t>
-        </is>
-      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
@@ -1291,16 +1335,62 @@
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>629000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>637000</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1308,7 +1398,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00407A,00993A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1321,52 +1411,16 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>奇鋐科技</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>奇鋐科技</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>2.40%</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1.66%</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>-0.74%</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>76000</v>
-      </c>
-      <c r="W6" t="n">
-        <v>52000</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-24,000</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1399,50 +1453,96 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>107000</v>
+        <v>513000</v>
       </c>
       <c r="BA6" t="n">
-        <v>105000</v>
+        <v>441000</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-72,000</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2.28%</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2.22%</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>198000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>2,000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1450,7 +1550,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00407A,00985A</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -1463,62 +1563,62 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>聯亞光電工業</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>聯亞光電工業</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>0.66%</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>-0.34%</t>
-        </is>
-      </c>
-      <c r="V7" t="n">
-        <v>31000</v>
-      </c>
-      <c r="W7" t="n">
-        <v>22000</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-9,000</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>南亞科技</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>南亞科技</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>-0.47%</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>193000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>105000</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>-88,000</t>
+        </is>
+      </c>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
@@ -1536,55 +1636,65 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>46000</v>
+        <v>595000</v>
       </c>
       <c r="BA7" t="n">
-        <v>47000</v>
+        <v>485000</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1,000</t>
-        </is>
-      </c>
+          <t>-110,000</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1592,7 +1702,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
+          <t>00403A,00985A</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1605,128 +1715,138 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1.92%</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>1.29%</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>-0.63%</t>
-        </is>
-      </c>
-      <c r="AP8" t="n">
-        <v>979000</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>696000</v>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-283,000</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3.69%</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3.39%</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>810000</v>
+      </c>
+      <c r="W8" t="n">
+        <v>736000</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>-74,000</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>1.93%</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1.88%</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>390000</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>401000</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>11,000</t>
-        </is>
-      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>-1.12%</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>16000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>-15,000</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1734,7 +1854,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
+          <t>00985A,00993A</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -1757,100 +1877,128 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>0.66%</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>+0.50%</t>
-        </is>
-      </c>
-      <c r="AP9" t="n">
-        <v>12000</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>49000</v>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>37,000</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>奇鋐科技</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>奇鋐科技</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2.40%</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1.66%</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>-0.74%</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>76000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>52000</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>-24,000</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>精測</t>
-        </is>
-      </c>
+      <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>0.54%</t>
-        </is>
-      </c>
+      <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="n">
-        <v>16000</v>
-      </c>
+      <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>107000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>105000</v>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1858,55 +2006,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00981A,00993A</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.14%</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>+0.10%</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>54000</v>
-      </c>
-      <c r="M10" t="n">
-        <v>95000</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>41,000</t>
-        </is>
-      </c>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -1917,16 +2029,52 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>聯亞光電工業</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>聯亞光電工業</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>-0.34%</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>31000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>22000</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>-9,000</t>
+        </is>
+      </c>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
@@ -1937,62 +2085,72 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr">
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>2.34%</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>2.26%</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>34000</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>32000</v>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-2,000</t>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>1.53%</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>46000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>47000</v>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>1,000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2000,7 +2158,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00992A,00993A</t>
+          <t>00407A,00993A</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -2023,52 +2181,16 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1.38%</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>2.61%</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>+1.23%</t>
-        </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>229675</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>429675</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>200,000</t>
-        </is>
-      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
@@ -2091,50 +2213,96 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>140191</v>
+        <v>979000</v>
       </c>
       <c r="BA11" t="n">
-        <v>134191</v>
+        <v>696000</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>-283,000</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>390000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>401000</v>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>11,000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>高力熱處理工業</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2142,7 +2310,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00407A,00993A</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -2155,52 +2323,16 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>高力熱處理工業</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>高力熱處理工業</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>1.36%</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>0.87%</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>-0.49%</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>113000</v>
-      </c>
-      <c r="W12" t="n">
-        <v>76000</v>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>-37,000</t>
-        </is>
-      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
@@ -2233,36 +2365,520 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>+0.50%</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>49000</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>37,000</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="n">
+        <v>16000</v>
+      </c>
+      <c r="BL12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>54000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>41,000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2.34%</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="BJ13" t="n">
+        <v>34000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>32000</v>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00992A,00993A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>2.61%</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>+1.23%</t>
+        </is>
+      </c>
+      <c r="AP14" t="n">
+        <v>229675</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>429675</v>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>200,000</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="BJ14" t="n">
+        <v>140191</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>134191</v>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>-6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>高力熱處理工業</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00985A,00993A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>高力熱處理工業</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>高力熱處理工業</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>-0.49%</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>113000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>76000</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>-37,000</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="AV12" t="inlineStr">
+      <c r="BF15" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>1.51%</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BH15" t="inlineStr">
         <is>
           <t>1.53%</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
+      <c r="BI15" t="inlineStr">
         <is>
           <t>+0.02%</t>
         </is>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BJ15" t="n">
         <v>122000</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BK15" t="n">
         <v>128000</v>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BL15" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>

--- a/etf_holdings/2026-09-04_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-04_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL15"/>
+  <dimension ref="A1:BB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,250 +489,200 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>00403A_異動類型</t>
+          <t>00985A_異動類型</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>00403A_調整方向</t>
+          <t>00985A_調整方向</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>00403A_股票名稱_昨日</t>
+          <t>00985A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>00403A_股票名稱_今日</t>
+          <t>00985A_股票名稱_今日</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>00403A_權重_昨日</t>
+          <t>00985A_權重_昨日</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>00403A_權重_今日</t>
+          <t>00985A_權重_今日</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>00403A_權重變化</t>
+          <t>00985A_權重變化</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>00403A_股數_昨日</t>
+          <t>00985A_股數_昨日</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>00403A_股數_今日</t>
+          <t>00985A_股數_今日</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>00403A_股數變化</t>
+          <t>00985A_股數變化</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>00985A_異動類型</t>
+          <t>00992A_異動類型</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>00985A_調整方向</t>
+          <t>00992A_調整方向</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>00985A_股票名稱_昨日</t>
+          <t>00992A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>00985A_股票名稱_今日</t>
+          <t>00992A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>00985A_權重_昨日</t>
+          <t>00992A_權重_昨日</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>00985A_權重_今日</t>
+          <t>00992A_權重_今日</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>00985A_權重變化</t>
+          <t>00992A_權重變化</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>00985A_股數_昨日</t>
+          <t>00992A_股數_昨日</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>00985A_股數_今日</t>
+          <t>00992A_股數_今日</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>00985A_股數變化</t>
+          <t>00992A_股數變化</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>00992A_異動類型</t>
+          <t>00407A_異動類型</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>00992A_調整方向</t>
+          <t>00407A_調整方向</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>00992A_股票名稱_昨日</t>
+          <t>00407A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>00992A_股票名稱_今日</t>
+          <t>00407A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>00992A_權重_昨日</t>
+          <t>00407A_權重_昨日</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>00992A_權重_今日</t>
+          <t>00407A_權重_今日</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>00992A_權重變化</t>
+          <t>00407A_權重變化</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>00992A_股數_昨日</t>
+          <t>00407A_股數_昨日</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>00992A_股數_今日</t>
+          <t>00407A_股數_今日</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>00992A_股數變化</t>
+          <t>00407A_股數變化</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>00407A_異動類型</t>
+          <t>00993A_異動類型</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>00407A_調整方向</t>
+          <t>00993A_調整方向</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>00407A_股票名稱_昨日</t>
+          <t>00993A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>00407A_股票名稱_今日</t>
+          <t>00993A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>00407A_權重_昨日</t>
+          <t>00993A_權重_昨日</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>00407A_權重_今日</t>
+          <t>00993A_權重_今日</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>00407A_權重變化</t>
+          <t>00993A_權重變化</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>00407A_股數_昨日</t>
+          <t>00993A_股數_昨日</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>00407A_股數_今日</t>
+          <t>00993A_股數_今日</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
-        <is>
-          <t>00407A_股數變化</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>00993A_異動類型</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>00993A_調整方向</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>00993A_股票名稱_昨日</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>00993A_股票名稱_今日</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>00993A_權重_昨日</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>00993A_權重_今日</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>00993A_權重變化</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>00993A_股數_昨日</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>00993A_股數_今日</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
         <is>
           <t>00993A_股數變化</t>
         </is>
@@ -803,62 +753,62 @@
           <t>20,000</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>健策精密工業</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>健策精密工業</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>1.48%</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.98%</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>-0.50%</t>
         </is>
       </c>
-      <c r="AF2" t="n">
+      <c r="V2" t="n">
         <v>27000</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="W2" t="n">
         <v>18000</v>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>-9,000</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
@@ -869,58 +819,48 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>健策</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>健策</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>1.30%</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>1.25%</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>-0.05%</t>
         </is>
       </c>
-      <c r="BJ2" t="n">
+      <c r="AZ2" t="n">
         <v>23000</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BA2" t="n">
         <v>22000</v>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>-1,000</t>
         </is>
@@ -929,12 +869,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -942,7 +882,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00403A,00407A</t>
+          <t>00985A,00993A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -967,38 +907,38 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>300000</v>
+        <v>383000</v>
       </c>
       <c r="W3" t="n">
-        <v>191000</v>
+        <v>295000</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-109,000</t>
+          <t>-88,000</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -1028,65 +968,55 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>177000</v>
+        <v>167000</v>
       </c>
       <c r="BA3" t="n">
-        <v>277000</v>
+        <v>165000</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>100,000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
+          <t>-2,000</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1094,7 +1024,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00407A,00993A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1117,128 +1047,118 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>國巨</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>國巨</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1.97%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>1.46%</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>-0.51%</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>383000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>295000</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-88,000</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>2.33%</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>1.94%</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>-0.39%</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>513000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>441000</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-72,000</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>0.88%</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>0.85%</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>-0.03%</t>
-        </is>
-      </c>
-      <c r="BJ4" t="n">
-        <v>167000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>165000</v>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>-2,000</t>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>2.28%</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>2.22%</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>198000</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>2,000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1246,7 +1166,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00403A,00993A</t>
+          <t>00407A,00985A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1271,38 +1191,38 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>2000000</v>
+        <v>193000</v>
       </c>
       <c r="W5" t="n">
-        <v>1000000</v>
+        <v>105000</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-1,000,000</t>
+          <t>-88,000</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1315,16 +1235,52 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>595000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>485000</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-110,000</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="inlineStr"/>
@@ -1335,62 +1291,16 @@
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>0.76%</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>0.75%</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="BJ5" t="n">
-        <v>629000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>637000</v>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>8,000</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1398,7 +1308,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
+          <t>00985A,00993A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1411,16 +1321,52 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>奇鋐科技</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>奇鋐科技</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2.40%</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1.66%</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>-0.74%</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>76000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>52000</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-24,000</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1453,96 +1399,50 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>513000</v>
+        <v>107000</v>
       </c>
       <c r="BA6" t="n">
-        <v>441000</v>
+        <v>105000</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-72,000</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>金像電子</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>金像電子</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2.28%</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2.22%</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>-0.06%</t>
-        </is>
-      </c>
-      <c r="BJ6" t="n">
-        <v>198000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>2,000</t>
+          <t>-2,000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1550,7 +1450,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00407A,00985A</t>
+          <t>00985A,00993A</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -1563,62 +1463,62 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>南亞科技</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>南亞科技</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.95%</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>0.48%</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>-0.47%</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>193000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>105000</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>-88,000</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>聯亞光電工業</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>聯亞光電工業</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>-0.34%</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>31000</v>
+      </c>
+      <c r="W7" t="n">
+        <v>22000</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-9,000</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
@@ -1636,65 +1536,55 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>595000</v>
+        <v>46000</v>
       </c>
       <c r="BA7" t="n">
-        <v>485000</v>
+        <v>47000</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-110,000</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
+          <t>1,000</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1702,7 +1592,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00403A,00985A</t>
+          <t>00407A,00993A</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1715,138 +1605,128 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>3.69%</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>3.39%</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>-0.30%</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>810000</v>
-      </c>
-      <c r="W8" t="n">
-        <v>736000</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>-74,000</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>1.92%</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>-0.63%</t>
+        </is>
+      </c>
+      <c r="AP8" t="n">
+        <v>979000</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>696000</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-283,000</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>大立光電</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>大立光電</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1.19%</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>0.07%</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>-1.12%</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>16000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>-15,000</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>390000</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>401000</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1854,7 +1734,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
+          <t>00407A,00993A</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -1877,128 +1757,100 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>奇鋐科技</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>奇鋐科技</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2.40%</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1.66%</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>-0.74%</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>76000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>52000</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-24,000</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>+0.50%</t>
+        </is>
+      </c>
+      <c r="AP9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>49000</v>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>37,000</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
       <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
       <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>16000</v>
+      </c>
       <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>3.46%</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>3.50%</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
-      <c r="BJ9" t="n">
-        <v>107000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>105000</v>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>-2,000</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2006,19 +1858,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00985A,00993A</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>54000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>95000</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>41,000</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -2029,52 +1917,16 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>聯亞光電工業</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>聯亞光電工業</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>0.66%</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>-0.34%</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>31000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>22000</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-9,000</t>
-        </is>
-      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
@@ -2085,72 +1937,62 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>聯亞光電</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>聯亞光電</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>1.53%</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>1.48%</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="BJ10" t="n">
-        <v>46000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>47000</v>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>1,000</t>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2.34%</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>34000</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>32000</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-2,000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2158,7 +2000,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
+          <t>00992A,00993A</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -2181,16 +2023,52 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2.61%</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>+1.23%</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
+        <v>229675</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>429675</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>200,000</t>
+        </is>
+      </c>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
@@ -2213,96 +2091,50 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>979000</v>
+        <v>140191</v>
       </c>
       <c r="BA11" t="n">
-        <v>696000</v>
+        <v>134191</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-283,000</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>1.93%</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>1.88%</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="BJ11" t="n">
-        <v>390000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>401000</v>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>11,000</t>
+          <t>-6,000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>高力熱處理工業</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2310,7 +2142,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
+          <t>00985A,00993A</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -2323,16 +2155,52 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>高力熱處理工業</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>高力熱處理工業</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>-0.49%</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>113000</v>
+      </c>
+      <c r="W12" t="n">
+        <v>76000</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>-37,000</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
@@ -2365,520 +2233,36 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>12000</v>
+        <v>122000</v>
       </c>
       <c r="BA12" t="n">
-        <v>49000</v>
+        <v>128000</v>
       </c>
       <c r="BB12" t="inlineStr">
-        <is>
-          <t>37,000</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>0.54%</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="n">
-        <v>16000</v>
-      </c>
-      <c r="BL12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>00981A,00993A</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.14%</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>+0.10%</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>54000</v>
-      </c>
-      <c r="M13" t="n">
-        <v>95000</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>41,000</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2.34%</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>2.26%</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
-      <c r="BJ13" t="n">
-        <v>34000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>32000</v>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>-2,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>00992A,00993A</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>1.38%</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>2.61%</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>+1.23%</t>
-        </is>
-      </c>
-      <c r="AP14" t="n">
-        <v>229675</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>429675</v>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>200,000</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>3.58%</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>3.35%</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>-0.23%</t>
-        </is>
-      </c>
-      <c r="BJ14" t="n">
-        <v>140191</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>134191</v>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>-6,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>高力熱處理工業</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>00985A,00993A</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>高力熱處理工業</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>高力熱處理工業</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1.36%</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>0.87%</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>-0.49%</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>113000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>76000</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>-37,000</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>1.51%</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>1.53%</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="BJ15" t="n">
-        <v>122000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>128000</v>
-      </c>
-      <c r="BL15" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
